--- a/data/trans_orig/P2A_ner_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2A_ner_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2007</t>
+          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7933</t>
+          <t>7327</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23912</t>
+          <t>23138</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23322</t>
+          <t>23385</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45692</t>
+          <t>45853</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36143</t>
+          <t>35357</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63548</t>
+          <t>60633</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>670100</t>
+          <t>670874</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>686079</t>
+          <t>686685</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>642659</t>
+          <t>642498</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>665029</t>
+          <t>664966</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1318815</t>
+          <t>1321730</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1346220</t>
+          <t>1347006</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,44%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19245</t>
+          <t>20676</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42150</t>
+          <t>42125</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33120</t>
+          <t>33151</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60297</t>
+          <t>59478</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57734</t>
+          <t>59361</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>93412</t>
+          <t>92477</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>919650</t>
+          <t>919675</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>942555</t>
+          <t>941124</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>908096</t>
+          <t>908915</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>935273</t>
+          <t>935242</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1836781</t>
+          <t>1837716</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1872459</t>
+          <t>1870832</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,92%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16262</t>
+          <t>15791</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>35953</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22863</t>
+          <t>23705</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44470</t>
+          <t>46020</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44401</t>
+          <t>45198</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73487</t>
+          <t>75255</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>643509</t>
+          <t>642556</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>662247</t>
+          <t>662718</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>639371</t>
+          <t>637821</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>660978</t>
+          <t>660136</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1288863</t>
+          <t>1287095</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1317949</t>
+          <t>1317152</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,68%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15369</t>
+          <t>15348</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33073</t>
+          <t>33992</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32834</t>
+          <t>31991</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59166</t>
+          <t>59902</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51603</t>
+          <t>50764</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84211</t>
+          <t>81536</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>909149</t>
+          <t>908230</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>926853</t>
+          <t>926874</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>979446</t>
+          <t>978710</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1005778</t>
+          <t>1006621</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1896623</t>
+          <t>1899298</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1929231</t>
+          <t>1930070</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,44%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>72645</t>
+          <t>73626</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>111320</t>
+          <t>110999</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>129417</t>
+          <t>132695</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>181201</t>
+          <t>182661</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>216538</t>
+          <t>217358</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>278899</t>
+          <t>277457</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3165223</t>
+          <t>3165544</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3203898</t>
+          <t>3202917</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3197996</t>
+          <t>3196536</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3249780</t>
+          <t>3246502</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6376842</t>
+          <t>6378284</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6439203</t>
+          <t>6438383</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,73%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2012</t>
+          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17809</t>
+          <t>17942</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39062</t>
+          <t>39525</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24742</t>
+          <t>23689</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47412</t>
+          <t>46157</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46354</t>
+          <t>47344</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>78946</t>
+          <t>77330</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>664407</t>
+          <t>663944</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>685660</t>
+          <t>685527</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>649638</t>
+          <t>650893</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>672308</t>
+          <t>673361</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1321573</t>
+          <t>1323189</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1354165</t>
+          <t>1353175</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,62%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14608</t>
+          <t>15493</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33758</t>
+          <t>34115</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40882</t>
+          <t>39741</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70844</t>
+          <t>70349</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>59663</t>
+          <t>60462</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>96430</t>
+          <t>98359</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>984189</t>
+          <t>983832</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1003339</t>
+          <t>1002454</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>961340</t>
+          <t>961835</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>991302</t>
+          <t>992443</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1953701</t>
+          <t>1951772</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1990468</t>
+          <t>1989669</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,05%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9790</t>
+          <t>9783</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28686</t>
+          <t>29187</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25803</t>
+          <t>27142</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49405</t>
+          <t>50270</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40094</t>
+          <t>40411</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70092</t>
+          <t>70257</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>728937</t>
+          <t>728436</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>747833</t>
+          <t>747840</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>727769</t>
+          <t>726904</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>751371</t>
+          <t>750032</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1464705</t>
+          <t>1464540</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1494703</t>
+          <t>1494386</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28413</t>
+          <t>27652</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53711</t>
+          <t>53814</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37521</t>
+          <t>37327</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67160</t>
+          <t>65449</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>73206</t>
+          <t>72275</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>112189</t>
+          <t>111072</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>894028</t>
+          <t>893925</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>919326</t>
+          <t>920087</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>984741</t>
+          <t>986452</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1014380</t>
+          <t>1014574</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1887451</t>
+          <t>1888568</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1926434</t>
+          <t>1927365</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,39%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>84953</t>
+          <t>87233</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>125556</t>
+          <t>129412</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>152205</t>
+          <t>150646</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>207429</t>
+          <t>204182</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>247516</t>
+          <t>250421</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>314833</t>
+          <t>316364</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3301223</t>
+          <t>3297367</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3341826</t>
+          <t>3339546</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3350880</t>
+          <t>3354127</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3406104</t>
+          <t>3407663</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6670255</t>
+          <t>6668724</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6737572</t>
+          <t>6734667</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,41%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2016</t>
+          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17172</t>
+          <t>17706</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37456</t>
+          <t>38486</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>63396</t>
+          <t>65738</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>97802</t>
+          <t>99035</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>88332</t>
+          <t>88644</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>127041</t>
+          <t>127625</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>637344</t>
+          <t>636314</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>657628</t>
+          <t>657094</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>575037</t>
+          <t>573804</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>609443</t>
+          <t>607101</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1220598</t>
+          <t>1220014</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1259307</t>
+          <t>1258995</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,42%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30402</t>
+          <t>31276</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56728</t>
+          <t>55890</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77508</t>
+          <t>77773</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>116405</t>
+          <t>116519</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>116537</t>
+          <t>117005</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>164047</t>
+          <t>162525</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>965703</t>
+          <t>966541</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>992029</t>
+          <t>991155</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>926508</t>
+          <t>926394</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>965405</t>
+          <t>965140</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1901297</t>
+          <t>1902819</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1948807</t>
+          <t>1948339</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,33%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23438</t>
+          <t>23214</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46858</t>
+          <t>46890</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>64393</t>
+          <t>65302</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>100991</t>
+          <t>99355</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>94145</t>
+          <t>95470</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>136288</t>
+          <t>136077</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>712694</t>
+          <t>712662</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>736114</t>
+          <t>736338</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>684020</t>
+          <t>685656</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>720618</t>
+          <t>719709</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1408275</t>
+          <t>1408486</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1450418</t>
+          <t>1449093</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,82%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38377</t>
+          <t>38877</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66745</t>
+          <t>68096</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>111346</t>
+          <t>109920</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>157595</t>
+          <t>158543</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>156103</t>
+          <t>158051</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>212407</t>
+          <t>210797</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>870822</t>
+          <t>869471</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>899190</t>
+          <t>898690</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>886184</t>
+          <t>885236</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>932433</t>
+          <t>933859</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1768939</t>
+          <t>1770549</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1825243</t>
+          <t>1823295</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,02%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>130162</t>
+          <t>129217</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>179186</t>
+          <t>177646</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>354888</t>
+          <t>351692</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>430916</t>
+          <t>431385</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>495007</t>
+          <t>502869</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>591483</t>
+          <t>592778</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3215164</t>
+          <t>3216704</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3264188</t>
+          <t>3265133</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3113626</t>
+          <t>3113157</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3189654</t>
+          <t>3192850</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6347409</t>
+          <t>6346114</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6443885</t>
+          <t>6436023</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,75%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2023</t>
+          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17274</t>
+          <t>17470</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37037</t>
+          <t>38390</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19111</t>
+          <t>18702</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36249</t>
+          <t>36852</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40084</t>
+          <t>40601</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67843</t>
+          <t>66213</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>598404</t>
+          <t>597051</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>618167</t>
+          <t>617971</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>689081</t>
+          <t>688478</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>706219</t>
+          <t>706628</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1292929</t>
+          <t>1294559</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1320688</t>
+          <t>1320171</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,02%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13808</t>
+          <t>14018</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42872</t>
+          <t>41757</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38551</t>
+          <t>39107</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60586</t>
+          <t>61125</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>54077</t>
+          <t>50635</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>96120</t>
+          <t>95137</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1149992</t>
+          <t>1151107</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1179056</t>
+          <t>1178846</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>898065</t>
+          <t>897526</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>920100</t>
+          <t>919544</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2055396</t>
+          <t>2056379</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2097439</t>
+          <t>2100881</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,65%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14632</t>
+          <t>15642</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34312</t>
+          <t>35871</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40098</t>
+          <t>40732</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>543040</t>
+          <t>576943</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62649</t>
+          <t>62066</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>715006</t>
+          <t>705072</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,04%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>670368</t>
+          <t>668809</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>690048</t>
+          <t>689038</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>390326</t>
+          <t>356423</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>893268</t>
+          <t>892634</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>923040</t>
+          <t>932974</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1575397</t>
+          <t>1575980</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24503</t>
+          <t>24143</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53251</t>
+          <t>53624</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35913</t>
+          <t>35782</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58340</t>
+          <t>59599</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>67200</t>
+          <t>68470</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103753</t>
+          <t>104653</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>873580</t>
+          <t>873207</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>902328</t>
+          <t>902688</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1036592</t>
+          <t>1035333</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1059019</t>
+          <t>1059150</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1918010</t>
+          <t>1917110</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1954563</t>
+          <t>1953293</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,61%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>88845</t>
+          <t>82858</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>141740</t>
+          <t>137277</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>161276</t>
+          <t>161437</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>988032</t>
+          <t>979354</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>268313</t>
+          <t>271451</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1189282</t>
+          <t>1132535</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>15,79%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3318077</t>
+          <t>3322540</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3370972</t>
+          <t>3376959</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2724248</t>
+          <t>2732926</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3551004</t>
+          <t>3550843</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5982815</t>
+          <t>6039562</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6903784</t>
+          <t>6900646</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,22%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2A_ner_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2A_ner_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7327</t>
+          <t>8525</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23138</t>
+          <t>24375</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23385</t>
+          <t>23246</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45853</t>
+          <t>45593</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35357</t>
+          <t>35066</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60633</t>
+          <t>62237</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>670874</t>
+          <t>669637</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>686685</t>
+          <t>685487</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>642498</t>
+          <t>642758</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>664966</t>
+          <t>665105</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1321730</t>
+          <t>1320126</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1347006</t>
+          <t>1347297</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,46%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20676</t>
+          <t>20022</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42125</t>
+          <t>41729</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33151</t>
+          <t>32235</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>59478</t>
+          <t>58949</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>59361</t>
+          <t>58040</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>92477</t>
+          <t>92860</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>919675</t>
+          <t>920071</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>941124</t>
+          <t>941778</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>908915</t>
+          <t>909444</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>935242</t>
+          <t>936158</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1837716</t>
+          <t>1837333</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1870832</t>
+          <t>1872153</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,99%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15791</t>
+          <t>16327</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35953</t>
+          <t>34848</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23705</t>
+          <t>22605</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46020</t>
+          <t>44430</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45198</t>
+          <t>44447</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75255</t>
+          <t>73818</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>642556</t>
+          <t>643661</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>662718</t>
+          <t>662182</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>637821</t>
+          <t>639411</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>660136</t>
+          <t>661236</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1287095</t>
+          <t>1288532</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1317152</t>
+          <t>1317903</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,74%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15348</t>
+          <t>14413</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33992</t>
+          <t>33026</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31991</t>
+          <t>32294</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59902</t>
+          <t>59302</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50764</t>
+          <t>51506</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>81536</t>
+          <t>85707</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>908230</t>
+          <t>909196</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>926874</t>
+          <t>927809</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>978710</t>
+          <t>979310</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1006621</t>
+          <t>1006318</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1899298</t>
+          <t>1895127</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1930070</t>
+          <t>1929328</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>73626</t>
+          <t>74179</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>110999</t>
+          <t>109749</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>132695</t>
+          <t>129995</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>182661</t>
+          <t>181669</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>217358</t>
+          <t>215957</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>277457</t>
+          <t>278037</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3165544</t>
+          <t>3166794</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3202917</t>
+          <t>3202364</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3196536</t>
+          <t>3197528</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3246502</t>
+          <t>3249202</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6378284</t>
+          <t>6377704</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6438383</t>
+          <t>6439784</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,76%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17942</t>
+          <t>17954</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39525</t>
+          <t>37683</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23689</t>
+          <t>24350</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46157</t>
+          <t>46442</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47344</t>
+          <t>47142</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>77330</t>
+          <t>79379</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>663944</t>
+          <t>665786</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>685527</t>
+          <t>685515</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>650893</t>
+          <t>650608</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>673361</t>
+          <t>672700</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1323189</t>
+          <t>1321140</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1353175</t>
+          <t>1353377</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,63%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15493</t>
+          <t>14543</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34115</t>
+          <t>34415</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39741</t>
+          <t>41190</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70349</t>
+          <t>70680</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>60462</t>
+          <t>60596</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>98359</t>
+          <t>95145</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>983832</t>
+          <t>983532</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1002454</t>
+          <t>1003404</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>961835</t>
+          <t>961504</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>992443</t>
+          <t>990994</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1951772</t>
+          <t>1954986</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1989669</t>
+          <t>1989535</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,04%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9783</t>
+          <t>9937</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29187</t>
+          <t>27782</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27142</t>
+          <t>25402</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50270</t>
+          <t>50668</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40411</t>
+          <t>39813</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70257</t>
+          <t>69494</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>728436</t>
+          <t>729841</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>747840</t>
+          <t>747686</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>726904</t>
+          <t>726506</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>750032</t>
+          <t>751772</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1464540</t>
+          <t>1465303</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1494386</t>
+          <t>1494984</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,41%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27652</t>
+          <t>27146</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53814</t>
+          <t>52274</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37327</t>
+          <t>38130</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65449</t>
+          <t>66153</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>72275</t>
+          <t>71519</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>111072</t>
+          <t>110906</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>893925</t>
+          <t>895465</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>920087</t>
+          <t>920593</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>986452</t>
+          <t>985748</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1014574</t>
+          <t>1013771</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1888568</t>
+          <t>1888734</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1927365</t>
+          <t>1928121</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,42%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>87233</t>
+          <t>84969</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>129412</t>
+          <t>127591</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>150646</t>
+          <t>153299</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>204182</t>
+          <t>205236</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>250421</t>
+          <t>246593</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>316364</t>
+          <t>316238</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3297367</t>
+          <t>3299188</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3339546</t>
+          <t>3341810</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3354127</t>
+          <t>3353073</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3407663</t>
+          <t>3405010</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6668724</t>
+          <t>6668850</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6734667</t>
+          <t>6738495</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,47%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17706</t>
+          <t>18356</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38486</t>
+          <t>38087</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>65738</t>
+          <t>63388</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>99035</t>
+          <t>97621</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>88644</t>
+          <t>87632</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>127625</t>
+          <t>128089</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,5%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>636314</t>
+          <t>636713</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>657094</t>
+          <t>656444</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>573804</t>
+          <t>575218</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>607101</t>
+          <t>609451</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1220014</t>
+          <t>1219550</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1258995</t>
+          <t>1260007</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,5%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31276</t>
+          <t>30277</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55890</t>
+          <t>56024</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77773</t>
+          <t>78319</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>116519</t>
+          <t>116298</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>117005</t>
+          <t>114524</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>162525</t>
+          <t>163118</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>966541</t>
+          <t>966407</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>991155</t>
+          <t>992154</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>926394</t>
+          <t>926615</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>965140</t>
+          <t>964594</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1902819</t>
+          <t>1902226</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1948339</t>
+          <t>1950820</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,45%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23214</t>
+          <t>22462</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46890</t>
+          <t>47072</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>65302</t>
+          <t>65930</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>99355</t>
+          <t>101316</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>95470</t>
+          <t>94094</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>136077</t>
+          <t>136655</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>712662</t>
+          <t>712480</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>736338</t>
+          <t>737090</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>685656</t>
+          <t>683695</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>719709</t>
+          <t>719081</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1408486</t>
+          <t>1407908</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1449093</t>
+          <t>1450469</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,91%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38877</t>
+          <t>38300</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>68096</t>
+          <t>67475</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>109920</t>
+          <t>111306</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>158543</t>
+          <t>157277</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>158051</t>
+          <t>159691</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>210797</t>
+          <t>212492</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>869471</t>
+          <t>870092</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>898690</t>
+          <t>899267</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>885236</t>
+          <t>886502</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>933859</t>
+          <t>932473</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1770549</t>
+          <t>1768854</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1823295</t>
+          <t>1821655</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>91,94%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>129217</t>
+          <t>130715</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>177646</t>
+          <t>179509</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>351692</t>
+          <t>352922</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>431385</t>
+          <t>429414</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>502869</t>
+          <t>500698</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>592778</t>
+          <t>595868</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3216704</t>
+          <t>3214841</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3265133</t>
+          <t>3263635</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3113157</t>
+          <t>3115128</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3192850</t>
+          <t>3191620</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6346114</t>
+          <t>6343024</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6436023</t>
+          <t>6438194</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,78%</t>
         </is>
       </c>
     </row>
@@ -6569,27 +6569,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>25522</t>
+          <t>29330</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17470</t>
+          <t>19555</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38390</t>
+          <t>41715</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>27101</t>
+          <t>29342</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18702</t>
+          <t>20893</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36852</t>
+          <t>40375</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>52624</t>
+          <t>58673</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40601</t>
+          <t>46629</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66213</t>
+          <t>75645</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -6682,22 +6682,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>609919</t>
+          <t>661380</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>597051</t>
+          <t>648995</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>617971</t>
+          <t>671155</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>698229</t>
+          <t>704838</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>688478</t>
+          <t>693805</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>706628</t>
+          <t>713287</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1308148</t>
+          <t>1366216</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1294559</t>
+          <t>1349244</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1320171</t>
+          <t>1378260</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,73%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27175</t>
+          <t>28767</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14018</t>
+          <t>19016</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41757</t>
+          <t>42588</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,17 +6947,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>49096</t>
+          <t>54819</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39107</t>
+          <t>43515</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61125</t>
+          <t>68209</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>76271</t>
+          <t>83586</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50635</t>
+          <t>68078</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>95137</t>
+          <t>102863</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1165689</t>
+          <t>1020150</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1151107</t>
+          <t>1006329</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1178846</t>
+          <t>1029901</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,17 +7060,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>909555</t>
+          <t>1016655</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>897526</t>
+          <t>1003265</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>919544</t>
+          <t>1027959</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2075245</t>
+          <t>2036805</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2056379</t>
+          <t>2017528</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2100881</t>
+          <t>2052313</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>96,79%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>23916</t>
+          <t>27867</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15642</t>
+          <t>18318</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35871</t>
+          <t>39782</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,67 +7290,67 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>240338</t>
+          <t>42605</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40732</t>
+          <t>32396</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>576943</t>
+          <t>56178</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>3,99%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>6,92%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>70471</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>56116</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>89643</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
           <t>4,36%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>61,81%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>264254</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>62066</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>705072</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>16,13%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>680764</t>
+          <t>775206</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>668809</t>
+          <t>763291</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>689038</t>
+          <t>784755</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,67 +7403,67 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>693028</t>
+          <t>769654</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>356423</t>
+          <t>756081</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>892634</t>
+          <t>779863</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
+          <t>96,01%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1642</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1544861</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1525689</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1559216</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
           <t>95,64%</t>
         </is>
       </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1642</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1373792</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>932974</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1575980</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>83,87%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,53%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>36508</t>
+          <t>36210</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24143</t>
+          <t>25006</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53624</t>
+          <t>53677</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>47183</t>
+          <t>52962</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35782</t>
+          <t>43362</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59599</t>
+          <t>65228</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>83691</t>
+          <t>89172</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>68470</t>
+          <t>73514</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>104653</t>
+          <t>107108</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>890323</t>
+          <t>953852</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>873207</t>
+          <t>936385</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>902688</t>
+          <t>965056</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1047749</t>
+          <t>1066079</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1035333</t>
+          <t>1053813</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1059150</t>
+          <t>1075679</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1938072</t>
+          <t>2019932</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1917110</t>
+          <t>2001996</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1953293</t>
+          <t>2035590</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,51%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>113122</t>
+          <t>122174</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>82858</t>
+          <t>101698</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>137277</t>
+          <t>148500</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>363717</t>
+          <t>179728</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>161437</t>
+          <t>157768</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>979354</t>
+          <t>204755</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>476840</t>
+          <t>301902</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>271451</t>
+          <t>272941</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1132535</t>
+          <t>336245</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3346695</t>
+          <t>3410588</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3322540</t>
+          <t>3384262</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3376959</t>
+          <t>3431064</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3348563</t>
+          <t>3557226</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2732926</t>
+          <t>3532199</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3550843</t>
+          <t>3579186</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6695257</t>
+          <t>6967814</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6039562</t>
+          <t>6933471</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6900646</t>
+          <t>6996775</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">

--- a/data/trans_orig/P2A_ner_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2A_ner_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con problemas de nervios, depresión o trastorno mental en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con problemas de nervios, depresión o trastorno mental en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con problemas de nervios, depresión o trastorno mental en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con problemas de nervios, depresión o trastorno mental en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
